--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_27-05-2026.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_27-05-2026.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Recticel_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F68A4E9-1027-4FDB-BA1D-8D485A497B79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{626A1265-9C21-4F43-91F6-006362C745A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29040" yWindow="2880" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1815" yWindow="2250" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -769,9 +769,6 @@
     <t>£600.0</t>
   </si>
   <si>
-    <t>£128.34</t>
-  </si>
-  <si>
     <t>£836.5</t>
   </si>
   <si>
@@ -796,9 +793,6 @@
     <t>£670.45</t>
   </si>
   <si>
-    <t>£130.17</t>
-  </si>
-  <si>
     <t>£751.9</t>
   </si>
   <si>
@@ -833,6 +827,12 @@
   </si>
   <si>
     <t>£276.59</t>
+  </si>
+  <si>
+    <t>£641.7</t>
+  </si>
+  <si>
+    <t>£650.85</t>
   </si>
 </sst>
 </file>
@@ -1380,7 +1380,7 @@
         <v>50</v>
       </c>
       <c r="E4" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="F4" t="s">
         <v>51</v>
@@ -1828,7 +1828,7 @@
         <v>153</v>
       </c>
       <c r="E12" t="s">
-        <v>153</v>
+        <v>27</v>
       </c>
       <c r="F12" t="s">
         <v>154</v>
@@ -1940,7 +1940,7 @@
         <v>177</v>
       </c>
       <c r="E14" t="s">
-        <v>177</v>
+        <v>27</v>
       </c>
       <c r="F14" t="s">
         <v>178</v>
@@ -1996,7 +1996,7 @@
         <v>190</v>
       </c>
       <c r="E15" t="s">
-        <v>190</v>
+        <v>27</v>
       </c>
       <c r="F15" t="s">
         <v>191</v>
@@ -2102,7 +2102,7 @@
         <v>215</v>
       </c>
       <c r="C17" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D17" t="s">
         <v>31</v>
@@ -2164,7 +2164,7 @@
         <v>218</v>
       </c>
       <c r="E18" t="s">
-        <v>218</v>
+        <v>27</v>
       </c>
       <c r="F18" t="s">
         <v>27</v>
@@ -2220,7 +2220,7 @@
         <v>226</v>
       </c>
       <c r="E19" t="s">
-        <v>226</v>
+        <v>27</v>
       </c>
       <c r="F19" t="s">
         <v>27</v>
@@ -2276,7 +2276,7 @@
         <v>234</v>
       </c>
       <c r="E20" t="s">
-        <v>234</v>
+        <v>27</v>
       </c>
       <c r="F20" t="s">
         <v>27</v>
@@ -2332,7 +2332,7 @@
         <v>238</v>
       </c>
       <c r="E21" t="s">
-        <v>238</v>
+        <v>27</v>
       </c>
       <c r="F21" t="s">
         <v>27</v>
@@ -2388,7 +2388,7 @@
         <v>242</v>
       </c>
       <c r="E22" t="s">
-        <v>242</v>
+        <v>27</v>
       </c>
       <c r="F22" t="s">
         <v>27</v>
@@ -2462,36 +2462,36 @@
         <v>27</v>
       </c>
       <c r="K23" t="s">
+        <v>269</v>
+      </c>
+      <c r="L23" t="s">
+        <v>27</v>
+      </c>
+      <c r="M23" t="s">
         <v>249</v>
       </c>
-      <c r="L23" t="s">
-        <v>27</v>
-      </c>
-      <c r="M23" t="s">
+      <c r="N23" t="s">
         <v>250</v>
       </c>
-      <c r="N23" t="s">
+      <c r="O23" t="s">
         <v>251</v>
       </c>
-      <c r="O23" t="s">
+      <c r="P23" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>27</v>
+      </c>
+      <c r="R23" t="s">
         <v>252</v>
-      </c>
-      <c r="P23" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>27</v>
-      </c>
-      <c r="R23" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>253</v>
+      </c>
+      <c r="B24" t="s">
         <v>254</v>
-      </c>
-      <c r="B24" t="s">
-        <v>255</v>
       </c>
       <c r="C24" t="s">
         <v>246</v>
@@ -2506,11 +2506,11 @@
         <v>27</v>
       </c>
       <c r="G24" t="s">
+        <v>255</v>
+      </c>
+      <c r="H24" t="s">
         <v>256</v>
       </c>
-      <c r="H24" t="s">
-        <v>257</v>
-      </c>
       <c r="I24" t="s">
         <v>27</v>
       </c>
@@ -2518,7 +2518,7 @@
         <v>27</v>
       </c>
       <c r="K24" t="s">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="L24" t="s">
         <v>27</v>
@@ -2527,10 +2527,10 @@
         <v>31</v>
       </c>
       <c r="N24" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="O24" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="P24" t="s">
         <v>27</v>
@@ -2539,42 +2539,42 @@
         <v>27</v>
       </c>
       <c r="R24" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>259</v>
+      </c>
+      <c r="B25" t="s">
+        <v>260</v>
+      </c>
+      <c r="C25" t="s">
         <v>261</v>
       </c>
-      <c r="B25" t="s">
+      <c r="D25" t="s">
+        <v>261</v>
+      </c>
+      <c r="E25" t="s">
+        <v>261</v>
+      </c>
+      <c r="F25" t="s">
+        <v>27</v>
+      </c>
+      <c r="G25" t="s">
         <v>262</v>
       </c>
-      <c r="C25" t="s">
+      <c r="H25" t="s">
         <v>263</v>
       </c>
-      <c r="D25" t="s">
-        <v>263</v>
-      </c>
-      <c r="E25" t="s">
-        <v>263</v>
-      </c>
-      <c r="F25" t="s">
-        <v>27</v>
-      </c>
-      <c r="G25" t="s">
+      <c r="I25" t="s">
+        <v>27</v>
+      </c>
+      <c r="J25" t="s">
+        <v>27</v>
+      </c>
+      <c r="K25" t="s">
         <v>264</v>
-      </c>
-      <c r="H25" t="s">
-        <v>265</v>
-      </c>
-      <c r="I25" t="s">
-        <v>27</v>
-      </c>
-      <c r="J25" t="s">
-        <v>27</v>
-      </c>
-      <c r="K25" t="s">
-        <v>266</v>
       </c>
       <c r="L25" t="s">
         <v>27</v>
@@ -2583,19 +2583,19 @@
         <v>31</v>
       </c>
       <c r="N25" t="s">
+        <v>265</v>
+      </c>
+      <c r="O25" t="s">
+        <v>266</v>
+      </c>
+      <c r="P25" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>27</v>
+      </c>
+      <c r="R25" t="s">
         <v>267</v>
-      </c>
-      <c r="O25" t="s">
-        <v>268</v>
-      </c>
-      <c r="P25" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>27</v>
-      </c>
-      <c r="R25" t="s">
-        <v>269</v>
       </c>
     </row>
   </sheetData>
